--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_8.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_1</t>
+          <t>model_23_8_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.999148043321515</v>
+        <v>0.9977359984214502</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7718252334768294</v>
+        <v>0.7406523925131983</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9973208535590384</v>
+        <v>0.9914400161912125</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9869305957851938</v>
+        <v>0.9714810386160809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9951060275117477</v>
+        <v>0.9899432990639925</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005697038231928841</v>
+        <v>0.001344009136802988</v>
       </c>
       <c r="H2" t="n">
-        <v>1.525805714388634</v>
+        <v>0.1539599430374658</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01339501151313774</v>
+        <v>0.002569092693327485</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01771213999224761</v>
+        <v>0.005773170055532259</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01555359232114787</v>
+        <v>0.004171135201188144</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1899016157987843</v>
+        <v>0.01000989126079681</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07547872701582109</v>
+        <v>0.0366607301728019</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000475510704271</v>
+        <v>1.001044923805485</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07869201268738918</v>
+        <v>0.03822145335443154</v>
       </c>
       <c r="P2" t="n">
-        <v>144.3356176952368</v>
+        <v>165.2241964773756</v>
       </c>
       <c r="Q2" t="n">
-        <v>226.0002979614063</v>
+        <v>257.8587591673588</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_2</t>
+          <t>model_23_8_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9991078847183558</v>
+        <v>0.9977647941731802</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7717665838142298</v>
+        <v>0.7406044312634117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9970516674548009</v>
+        <v>0.9915536128398305</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9860566207359992</v>
+        <v>0.971907340184157</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9947079441528944</v>
+        <v>0.9900884409159292</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005965578996167813</v>
+        <v>0.001326914734664388</v>
       </c>
       <c r="H3" t="n">
-        <v>1.526197904952495</v>
+        <v>0.1539884149071573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01474086962313494</v>
+        <v>0.002534999133518255</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01889658330478436</v>
+        <v>0.005686872682556014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01681874579070673</v>
+        <v>0.004110935908037135</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1897929131830595</v>
+        <v>0.0101437915157831</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07723716072052243</v>
+        <v>0.03642684085484751</v>
       </c>
       <c r="N3" t="n">
-        <v>1.00049792480836</v>
+        <v>1.001031633458532</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08052530655535922</v>
+        <v>0.03797760688399421</v>
       </c>
       <c r="P3" t="n">
-        <v>144.2434983251313</v>
+        <v>165.2497975598113</v>
       </c>
       <c r="Q3" t="n">
-        <v>225.9081785913007</v>
+        <v>257.8843602497946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_0</t>
+          <t>model_23_8_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.998744196761552</v>
+        <v>0.9977960534206495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7717192511336948</v>
+        <v>0.7405490362852105</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9980693616182688</v>
+        <v>0.9916796185410416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9959655940545589</v>
+        <v>0.9723760899650947</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9976211900202453</v>
+        <v>0.9902484129742037</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00839756203794364</v>
+        <v>0.001308357895037406</v>
       </c>
       <c r="H4" t="n">
-        <v>1.52651441880518</v>
+        <v>0.1540212997591559</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009652672566010942</v>
+        <v>0.002497181266857478</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005467576158540921</v>
+        <v>0.00559198240368446</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007560124361834411</v>
+        <v>0.004044585612078085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2061536032484892</v>
+        <v>0.01029224779308174</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09163821276052715</v>
+        <v>0.03617123021183281</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000700913435413</v>
+        <v>1.001017206113546</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09553944119499434</v>
+        <v>0.03771111436671939</v>
       </c>
       <c r="P4" t="n">
-        <v>143.5596276976738</v>
+        <v>165.2779648866302</v>
       </c>
       <c r="Q4" t="n">
-        <v>225.2243079638433</v>
+        <v>257.9125275766135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_3</t>
+          <t>model_23_8_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9990658324435817</v>
+        <v>0.9978298281896969</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7717091442551358</v>
+        <v>0.7404848984381294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9967849379467202</v>
+        <v>0.9918192179684903</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9852340677640923</v>
+        <v>0.9728901962714022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9943227590743767</v>
+        <v>0.9904243749327428</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006246782751215256</v>
+        <v>0.00128830773313683</v>
       </c>
       <c r="H5" t="n">
-        <v>1.526582003548641</v>
+        <v>0.1540593747557941</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01607444541317402</v>
+        <v>0.002455283539354426</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0200113375162235</v>
+        <v>0.005487910481394616</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01804290708173024</v>
+        <v>0.003971603316591474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1897377290253968</v>
+        <v>0.01045726266855543</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07903659121707651</v>
+        <v>0.03589300395810903</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000521395845443</v>
+        <v>1.001001617758601</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08240134253348626</v>
+        <v>0.03742104344536684</v>
       </c>
       <c r="P5" t="n">
-        <v>144.1513774151474</v>
+        <v>165.3088515131894</v>
       </c>
       <c r="Q5" t="n">
-        <v>225.8160576813168</v>
+        <v>257.9434142031727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_4</t>
+          <t>model_23_8_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9990231514582216</v>
+        <v>0.9978662607704611</v>
       </c>
       <c r="C6" t="n">
-        <v>0.77165366272625</v>
+        <v>0.7404100582905728</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9965248072785202</v>
+        <v>0.991973860245455</v>
       </c>
       <c r="E6" t="n">
-        <v>0.984464168825831</v>
+        <v>0.9734546071567192</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9939540038236344</v>
+        <v>0.9906180715422596</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006532190696845905</v>
+        <v>0.001266679779389603</v>
       </c>
       <c r="H6" t="n">
-        <v>1.52695300878777</v>
+        <v>0.1541038031003096</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01737502877890013</v>
+        <v>0.002408871028220747</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02105473303374197</v>
+        <v>0.005373655267880226</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01921485254119022</v>
+        <v>0.003891265365662329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1897193344328211</v>
+        <v>0.01064022232664743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08082196914729253</v>
+        <v>0.03559044505748141</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00054521779076</v>
+        <v>1.000984802721326</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08426272769843338</v>
+        <v>0.03710560398595625</v>
       </c>
       <c r="P6" t="n">
-        <v>144.0620258200986</v>
+        <v>165.3427122976436</v>
       </c>
       <c r="Q6" t="n">
-        <v>225.7267060862681</v>
+        <v>257.9772749876269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_5</t>
+          <t>model_23_8_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9989807798377176</v>
+        <v>0.9979053032269984</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7716006687792282</v>
+        <v>0.740323202127082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9962742293006442</v>
+        <v>0.9921448804441735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9837467717000037</v>
+        <v>0.9740721084054702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9936039565736801</v>
+        <v>0.9908306452038995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006815529918259962</v>
+        <v>0.00124350249064275</v>
       </c>
       <c r="H7" t="n">
-        <v>1.527307379555519</v>
+        <v>0.1541553646709487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01862785126268414</v>
+        <v>0.002357543040603761</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02202697615315628</v>
+        <v>0.005248652829307776</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02032734188026967</v>
+        <v>0.003803097934955769</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1897263351310224</v>
+        <v>0.01084326659929571</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08255622277127243</v>
+        <v>0.03526333067993932</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000568867067321</v>
+        <v>1.000966783126001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08607081208958602</v>
+        <v>0.03676456367214207</v>
       </c>
       <c r="P7" t="n">
-        <v>143.9771029184498</v>
+        <v>165.3796465835868</v>
       </c>
       <c r="Q7" t="n">
-        <v>225.6417831846193</v>
+        <v>258.01420927357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_6</t>
+          <t>model_23_8_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9989394314434762</v>
+        <v>0.9979469784506323</v>
       </c>
       <c r="C8" t="n">
-        <v>0.771550481916366</v>
+        <v>0.7402216699180956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9960352915419555</v>
+        <v>0.9923341533614617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9830814359549267</v>
+        <v>0.9747472304382555</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9932741416112008</v>
+        <v>0.991063872441145</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007092026820943802</v>
+        <v>0.001218762277617772</v>
       </c>
       <c r="H8" t="n">
-        <v>1.527642979338568</v>
+        <v>0.1542156385761661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0198224757817571</v>
+        <v>0.002300736897074522</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02292866376377433</v>
+        <v>0.005111986060450474</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02137553074527263</v>
+        <v>0.003706364190426545</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1897581544291819</v>
+        <v>0.01106857510492307</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08421417232831896</v>
+        <v>0.03491077595267359</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00059194524085</v>
+        <v>1.0009475484074</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08779934399170473</v>
+        <v>0.03639699996024775</v>
       </c>
       <c r="P8" t="n">
-        <v>143.8975682178367</v>
+        <v>165.4198389235203</v>
       </c>
       <c r="Q8" t="n">
-        <v>225.5622484840061</v>
+        <v>258.0544016135036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_7</t>
+          <t>model_23_8_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9988995806273919</v>
+        <v>0.9979911895349776</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7715032273397353</v>
+        <v>0.7401023911554079</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9958092371065804</v>
+        <v>0.9925432701162755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9824662057658866</v>
+        <v>0.9754843898823463</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9929651498499524</v>
+        <v>0.9913194509944351</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007358509411595179</v>
+        <v>0.001192516668131049</v>
       </c>
       <c r="H9" t="n">
-        <v>1.527958970910084</v>
+        <v>0.1542864476022718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02095268714988154</v>
+        <v>0.002237975057934932</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02376244647158817</v>
+        <v>0.004962760891571179</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02235754114614567</v>
+        <v>0.003600359974224775</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1898001808201422</v>
+        <v>0.01131842075270941</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08578175453786882</v>
+        <v>0.03453283463793624</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000614187556804</v>
+        <v>1.000927143291549</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08943366142125767</v>
+        <v>0.03600296890129565</v>
       </c>
       <c r="P9" t="n">
-        <v>143.8237957847018</v>
+        <v>165.4633787156621</v>
       </c>
       <c r="Q9" t="n">
-        <v>225.4884760508712</v>
+        <v>258.0979414056454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_8</t>
+          <t>model_23_8_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9988615811241557</v>
+        <v>0.9980377498195666</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7714591489215433</v>
+        <v>0.7399619811428571</v>
       </c>
       <c r="D10" t="n">
-        <v>0.99559680817959</v>
+        <v>0.9927740862186355</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9818995147406832</v>
+        <v>0.9762879838300543</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9926772303023151</v>
+        <v>0.9915990477639596</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007612612264707938</v>
+        <v>0.001164876471899395</v>
       </c>
       <c r="H10" t="n">
-        <v>1.528253723495497</v>
+        <v>0.1543698010511187</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02201477464135148</v>
+        <v>0.002168700632267616</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02453044710924402</v>
+        <v>0.00480008720744708</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02327258169367423</v>
+        <v>0.003484393919857348</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1898538647410272</v>
+        <v>0.01159560149725233</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08725028518410664</v>
+        <v>0.03413028672454122</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000635396581867</v>
+        <v>1.000905653929431</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09096471045738333</v>
+        <v>0.03558328368983835</v>
       </c>
       <c r="P10" t="n">
-        <v>143.7558977972768</v>
+        <v>165.5102804605814</v>
       </c>
       <c r="Q10" t="n">
-        <v>225.4205780634462</v>
+        <v>258.1448431505647</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_9</t>
+          <t>model_23_8_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9988256221231807</v>
+        <v>0.9980863412237218</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7714181173912673</v>
+        <v>0.7397959497666338</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9953982797424726</v>
+        <v>0.9930285951753246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9813782827442145</v>
+        <v>0.9771621343739408</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9924099269370344</v>
+        <v>0.9919044543569565</v>
       </c>
       <c r="G11" t="n">
-        <v>0.007853070269803288</v>
+        <v>0.00113603051535357</v>
       </c>
       <c r="H11" t="n">
-        <v>1.528528101527385</v>
+        <v>0.1544683644482268</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0230073634226937</v>
+        <v>0.002092315312432627</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02523683998975763</v>
+        <v>0.004623130561794532</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02412210170622566</v>
+        <v>0.00335772293711358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1899150182584259</v>
+        <v>0.0119027269984858</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08861755057438277</v>
+        <v>0.03370505177793932</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000655466721946</v>
+        <v>1.000883227127513</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09239018316595306</v>
+        <v>0.03513994561120191</v>
       </c>
       <c r="P11" t="n">
-        <v>143.6937014129636</v>
+        <v>165.5604301938739</v>
       </c>
       <c r="Q11" t="n">
-        <v>225.3583816791331</v>
+        <v>258.1949928838571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_10</t>
+          <t>model_23_8_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9987918405096556</v>
+        <v>0.9981365381720619</v>
       </c>
       <c r="C12" t="n">
-        <v>0.771380118192878</v>
+        <v>0.7395991562324484</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9952136384565877</v>
+        <v>0.9933089247846744</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9809004511237089</v>
+        <v>0.9781120659334581</v>
       </c>
       <c r="F12" t="n">
-        <v>0.992162797753015</v>
+        <v>0.9922376952125146</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008078968074995635</v>
+        <v>0.00110623143842354</v>
       </c>
       <c r="H12" t="n">
-        <v>1.528782202341985</v>
+        <v>0.1545851895911572</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02393052018352436</v>
+        <v>0.002008180486106848</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0258844150755085</v>
+        <v>0.004430833361332566</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02490750591275212</v>
+        <v>0.003219507366029436</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1899769474871063</v>
+        <v>0.01224322429224502</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08988308002619645</v>
+        <v>0.03326005770325031</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000674321576006</v>
+        <v>1.000860059305202</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09370958882653756</v>
+        <v>0.03467600721748867</v>
       </c>
       <c r="P12" t="n">
-        <v>143.6369822561917</v>
+        <v>165.6135922812182</v>
       </c>
       <c r="Q12" t="n">
-        <v>225.3016625223611</v>
+        <v>258.2481549712014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_11</t>
+          <t>model_23_8_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9987602831057384</v>
+        <v>0.9981876700558477</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7713449966177456</v>
+        <v>0.7393645921834378</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9950426194865764</v>
+        <v>0.9936169567279182</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9804631918849984</v>
+        <v>0.9791423540827209</v>
       </c>
       <c r="F13" t="n">
-        <v>0.991935071080522</v>
+        <v>0.9926005628760469</v>
       </c>
       <c r="G13" t="n">
-        <v>0.008289992580298835</v>
+        <v>0.001075877343425936</v>
       </c>
       <c r="H13" t="n">
-        <v>1.529017060476615</v>
+        <v>0.1547244369432894</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02478556902939674</v>
+        <v>0.00191573140765337</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02647700496879308</v>
+        <v>0.004222269360287034</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02563124676603815</v>
+        <v>0.003069003727275196</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1900414485886452</v>
+        <v>0.01262030378031706</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09104939637525794</v>
+        <v>0.03280056925460191</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000691935010751</v>
+        <v>1.000836459974224</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09492555767718629</v>
+        <v>0.03419695739430909</v>
       </c>
       <c r="P13" t="n">
-        <v>143.5854124097071</v>
+        <v>165.6692376336777</v>
       </c>
       <c r="Q13" t="n">
-        <v>225.2500926758766</v>
+        <v>258.3038003236609</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9987309470084776</v>
+        <v>0.9982387096568257</v>
       </c>
       <c r="C14" t="n">
-        <v>0.771312738193812</v>
+        <v>0.7390844953139286</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9948847724256453</v>
+        <v>0.9939544213604399</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9800638341726061</v>
+        <v>0.9802561677298502</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9917257581387359</v>
+        <v>0.9929944777111159</v>
       </c>
       <c r="G14" t="n">
-        <v>0.008486163197761605</v>
+        <v>0.001045578031489475</v>
       </c>
       <c r="H14" t="n">
-        <v>1.529232772705996</v>
+        <v>0.1548907145445847</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02557476187311686</v>
+        <v>0.001814448748592983</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02701822931174062</v>
+        <v>0.003996797068064072</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0262964667221979</v>
+        <v>0.002905622908328527</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1901066686235228</v>
+        <v>0.01303799786712191</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09212037341305997</v>
+        <v>0.03233539904639303</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000708308646431</v>
+        <v>1.000812903235311</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09604212842471563</v>
+        <v>0.03371198392730168</v>
       </c>
       <c r="P14" t="n">
-        <v>143.53863660195</v>
+        <v>165.7263708126194</v>
       </c>
       <c r="Q14" t="n">
-        <v>225.2033168681194</v>
+        <v>258.3609335026026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_13</t>
+          <t>model_23_8_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9987037787573207</v>
+        <v>0.9982884869498506</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7712830701491262</v>
+        <v>0.738748285245395</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9947394526909665</v>
+        <v>0.994323254497216</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9796996911497521</v>
+        <v>0.9814591192952782</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9915337975914854</v>
+        <v>0.9934214867050654</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008667837418346109</v>
+        <v>0.00101602808008276</v>
       </c>
       <c r="H15" t="n">
-        <v>1.529431163057418</v>
+        <v>0.1550903033647849</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02630132145543332</v>
+        <v>0.001703751516224877</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02751172940493418</v>
+        <v>0.003753280347300864</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02690653882637203</v>
+        <v>0.00272851589707105</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1901672825366613</v>
+        <v>0.01351973558801684</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09310122135797204</v>
+        <v>0.03187519537324845</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000723472321495</v>
+        <v>1.000789929100069</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09706473309727777</v>
+        <v>0.03323218843103841</v>
       </c>
       <c r="P15" t="n">
-        <v>143.4962719040398</v>
+        <v>165.7837085846621</v>
       </c>
       <c r="Q15" t="n">
-        <v>225.1609521702092</v>
+        <v>258.4182712746453</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_14</t>
+          <t>model_23_8_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9986787054576437</v>
+        <v>0.9983352008908399</v>
       </c>
       <c r="C16" t="n">
-        <v>0.77125592859307</v>
+        <v>0.7383438170233334</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9946060697032982</v>
+        <v>0.9947247180045731</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9793679546003026</v>
+        <v>0.9827538653772505</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9913581478568384</v>
+        <v>0.9938827025236711</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008835502688738693</v>
+        <v>0.0009882966667743658</v>
       </c>
       <c r="H16" t="n">
-        <v>1.529612658767741</v>
+        <v>0.1553304131735181</v>
       </c>
       <c r="I16" t="n">
-        <v>0.02696820051368718</v>
+        <v>0.001583260988856127</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0279613110467461</v>
+        <v>0.003491181415669544</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02746477334251903</v>
+        <v>0.002537221202262835</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1902283929936383</v>
+        <v>0.01413350823783621</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09399735469011185</v>
+        <v>0.03143718605050977</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000737466721315</v>
+        <v>1.000768368819612</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09799901668061851</v>
+        <v>0.03277553214462644</v>
       </c>
       <c r="P16" t="n">
-        <v>143.4579545548107</v>
+        <v>165.8390552705478</v>
       </c>
       <c r="Q16" t="n">
-        <v>225.1226348209801</v>
+        <v>258.473617960531</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_15</t>
+          <t>model_23_8_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9986556472788101</v>
+        <v>0.9983766903117581</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7712311175759718</v>
+        <v>0.737855124095983</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9944838901604347</v>
+        <v>0.9951598697636036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9790666846697955</v>
+        <v>0.9841447713071152</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9911978149252803</v>
+        <v>0.9943795663527176</v>
       </c>
       <c r="G17" t="n">
-        <v>0.008989692836772404</v>
+        <v>0.000963666754267637</v>
       </c>
       <c r="H17" t="n">
-        <v>1.529778570153321</v>
+        <v>0.1556205224056287</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02757906536164974</v>
+        <v>0.001452659666518774</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02836960319969281</v>
+        <v>0.003209616587404631</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02797432934413045</v>
+        <v>0.00233114107511967</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1902853215019526</v>
+        <v>0.01480666242797662</v>
       </c>
       <c r="M17" t="n">
-        <v>0.09481399072274305</v>
+        <v>0.0310429823674794</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000750336402525</v>
+        <v>1.000749219856112</v>
       </c>
       <c r="O17" t="n">
-        <v>0.09885041859982843</v>
+        <v>0.03236454639469535</v>
       </c>
       <c r="P17" t="n">
-        <v>143.4233531965868</v>
+        <v>165.8895300274245</v>
       </c>
       <c r="Q17" t="n">
-        <v>225.0880334627562</v>
+        <v>258.5240927174077</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_16</t>
+          <t>model_23_8_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9986344769635335</v>
+        <v>0.9984098812212533</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7712084756385962</v>
+        <v>0.7372634446146427</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9943722402363889</v>
+        <v>0.9956284422791116</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9787925145540145</v>
+        <v>0.9856325232045493</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9910515324034362</v>
+        <v>0.9949121632988116</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00913125883250691</v>
+        <v>0.0009439631966186644</v>
       </c>
       <c r="H18" t="n">
-        <v>1.529929976892809</v>
+        <v>0.155971768904975</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02813728494799607</v>
+        <v>0.00131202783206953</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0287411686813774</v>
+        <v>0.002908446969454536</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02843923157109077</v>
+        <v>0.002110240216673787</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1903395497037459</v>
+        <v>0.01554391911920616</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09555762048370035</v>
+        <v>0.03072398406161975</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000762152392446</v>
+        <v>1.000733900974806</v>
       </c>
       <c r="O18" t="n">
-        <v>0.09962570621923553</v>
+        <v>0.03203196767053773</v>
       </c>
       <c r="P18" t="n">
-        <v>143.3921034303646</v>
+        <v>165.9308467584231</v>
       </c>
       <c r="Q18" t="n">
-        <v>225.056783696534</v>
+        <v>258.5654094484063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_17</t>
+          <t>model_23_8_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9986150923635734</v>
+        <v>0.9984308532953126</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7711878687554191</v>
+        <v>0.7365436927127509</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9942703172073059</v>
+        <v>0.9961292963961904</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9785438442828251</v>
+        <v>0.9872168473455457</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9909183115130906</v>
+        <v>0.9954800134519001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.009260883741697914</v>
+        <v>0.0009315132675106916</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5300677752155</v>
+        <v>0.1563990447256012</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02864687267606791</v>
+        <v>0.001161707378041424</v>
       </c>
       <c r="J19" t="n">
-        <v>0.02907817583050414</v>
+        <v>0.002587727972506262</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02886262247123799</v>
+        <v>0.001874717675273843</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1903881849829391</v>
+        <v>0.01634947315726903</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09623348555309588</v>
+        <v>0.03052070227748194</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000772971704052</v>
+        <v>1.000724221556009</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1003303442638688</v>
+        <v>0.03182003175999788</v>
       </c>
       <c r="P19" t="n">
-        <v>143.3639115968187</v>
+        <v>165.9574002497128</v>
       </c>
       <c r="Q19" t="n">
-        <v>225.0285918629882</v>
+        <v>258.591962939696</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_18</t>
+          <t>model_23_8_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9985973826573042</v>
+        <v>0.9984343141507273</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7711690885650686</v>
+        <v>0.7356664356149565</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9941775101339198</v>
+        <v>0.9966591658926001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9783182993731038</v>
+        <v>0.9888918428316802</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9907972672741914</v>
+        <v>0.9960804793116783</v>
       </c>
       <c r="G20" t="n">
-        <v>0.009379308629065629</v>
+        <v>0.000929458754235341</v>
       </c>
       <c r="H20" t="n">
-        <v>1.530193358434848</v>
+        <v>0.1569198224343854</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02911088307785142</v>
+        <v>0.001002678589897487</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02938384263442757</v>
+        <v>0.002248654131298433</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02924731461022749</v>
+        <v>0.001625667385246341</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1904339927773368</v>
+        <v>0.01722754058812658</v>
       </c>
       <c r="M20" t="n">
-        <v>0.09684683076417952</v>
+        <v>0.03048702599853487</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000782856191272</v>
+        <v>1.000722624238126</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1009698008503879</v>
+        <v>0.03178492181213652</v>
       </c>
       <c r="P20" t="n">
-        <v>143.3384984512063</v>
+        <v>165.961816251858</v>
       </c>
       <c r="Q20" t="n">
-        <v>225.0031787173757</v>
+        <v>258.5963789418412</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_19</t>
+          <t>model_23_8_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9985812241356561</v>
+        <v>0.9984132168806961</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7711520454751437</v>
+        <v>0.7345941520997337</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9940930632675509</v>
+        <v>0.99721204695098</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9781138778895956</v>
+        <v>0.9906432402317707</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9906872346385924</v>
+        <v>0.9967079261692587</v>
       </c>
       <c r="G21" t="n">
-        <v>0.009487360737729662</v>
+        <v>0.0009419830050804845</v>
       </c>
       <c r="H21" t="n">
-        <v>1.530307325655653</v>
+        <v>0.1575563762492577</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02953309469344823</v>
+        <v>0.0008367433826480678</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02966088218985103</v>
+        <v>0.001894114045163278</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02959701064146499</v>
+        <v>0.001365426408490453</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1904781533255869</v>
+        <v>0.0181820821223007</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09740308382042974</v>
+        <v>0.03069174164299714</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000791874901029</v>
+        <v>1.000732361439679</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1015497347508452</v>
+        <v>0.03199835262540335</v>
       </c>
       <c r="P21" t="n">
-        <v>143.3155896297366</v>
+        <v>165.935046649733</v>
       </c>
       <c r="Q21" t="n">
-        <v>224.980269895906</v>
+        <v>258.5696093397162</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_20</t>
+          <t>model_23_8_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9985665048460123</v>
+        <v>0.9983580668514639</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7711365788557761</v>
+        <v>0.733279676378465</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9940162736273791</v>
+        <v>0.9977780563723205</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9779289498767654</v>
+        <v>0.9924430152110899</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9905874015403715</v>
+        <v>0.9973519101686883</v>
       </c>
       <c r="G22" t="n">
-        <v>0.009585788695353918</v>
+        <v>0.0009747224447898936</v>
       </c>
       <c r="H22" t="n">
-        <v>1.530410751010581</v>
+        <v>0.1583367058197972</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02991702223785718</v>
+        <v>0.0006668679832077222</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02991150347280336</v>
+        <v>0.001529780755551944</v>
       </c>
       <c r="K22" t="n">
-        <v>0.02991429140134135</v>
+        <v>0.001098326457312133</v>
       </c>
       <c r="L22" t="n">
-        <v>0.19051898305465</v>
+        <v>0.01921633441972318</v>
       </c>
       <c r="M22" t="n">
-        <v>0.09790704109181279</v>
+        <v>0.03122054523530769</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000800090318505</v>
+        <v>1.000757815299324</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1020751465266064</v>
+        <v>0.0325496684814129</v>
       </c>
       <c r="P22" t="n">
-        <v>143.2949472430688</v>
+        <v>165.8667155990071</v>
       </c>
       <c r="Q22" t="n">
-        <v>224.9596275092382</v>
+        <v>258.5012782889904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_21</t>
+          <t>model_23_8_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9985531103677828</v>
+        <v>0.9982559606582421</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7711225426497321</v>
+        <v>0.7316642896686083</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9939465580131102</v>
+        <v>0.9983419289928898</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9777614923582242</v>
+        <v>0.99423862162731</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9904968687236491</v>
+        <v>0.9979941154808971</v>
       </c>
       <c r="G23" t="n">
-        <v>0.009675357632950375</v>
+        <v>0.001035337091844284</v>
       </c>
       <c r="H23" t="n">
-        <v>1.530504611185027</v>
+        <v>0.1592956691518407</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03026558155566845</v>
+        <v>0.0004976338979767791</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03013844809571089</v>
+        <v>0.001166291319380238</v>
       </c>
       <c r="K23" t="n">
-        <v>0.03020201482568967</v>
+        <v>0.0008319642376150645</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1905570728043676</v>
+        <v>0.02033296301338517</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09836339579818489</v>
+        <v>0.03217665445387826</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000807566306354</v>
+        <v>1.000804941234658</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1025509291976133</v>
+        <v>0.03354648124883695</v>
       </c>
       <c r="P23" t="n">
-        <v>143.2763461522069</v>
+        <v>165.7460564253759</v>
       </c>
       <c r="Q23" t="n">
-        <v>224.9410264183763</v>
+        <v>258.3806191153591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_22</t>
+          <t>model_23_8_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9985409381590177</v>
+        <v>0.9980889461018493</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7711097848474835</v>
+        <v>0.7296759137804802</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9938833061158427</v>
+        <v>0.9988809175551473</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9776100814028282</v>
+        <v>0.9959344451468685</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9904148113184915</v>
+        <v>0.9986029660947348</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0097567532490111</v>
+        <v>0.001134484147172176</v>
       </c>
       <c r="H24" t="n">
-        <v>1.530589922667408</v>
+        <v>0.1604760549723995</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03058182402721511</v>
+        <v>0.0003358682208429747</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03034364582272709</v>
+        <v>0.0008230012033487874</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03046280244348168</v>
+        <v>0.000579436272052295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1905904770185766</v>
+        <v>0.02153456938505887</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09877627877689613</v>
+        <v>0.0336821042568925</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000814360097293</v>
+        <v>1.000882024876069</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1029813894595138</v>
+        <v>0.03511602116667621</v>
       </c>
       <c r="P24" t="n">
-        <v>143.2595911856264</v>
+        <v>165.5631544544937</v>
       </c>
       <c r="Q24" t="n">
-        <v>224.9242714517958</v>
+        <v>258.197717144477</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_23</t>
+          <t>model_23_8_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9985298839924548</v>
+        <v>0.9978323089343885</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7710982510170438</v>
+        <v>0.7272218686745174</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9938259564050952</v>
+        <v>0.9993625161969202</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9774731585810034</v>
+        <v>0.9973718519991326</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9903405481875561</v>
+        <v>0.9991279905010348</v>
       </c>
       <c r="G25" t="n">
-        <v>0.009830672511716784</v>
+        <v>0.001286835055925309</v>
       </c>
       <c r="H25" t="n">
-        <v>1.530667049444667</v>
+        <v>0.1619328821565277</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03086855715385335</v>
+        <v>0.0001913268783202138</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03052920869525244</v>
+        <v>0.0005320230682969551</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03069881898542876</v>
+        <v>0.0003616762137055085</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1906209995653532</v>
+        <v>0.02282147597954666</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09914974791554834</v>
+        <v>0.03587248326956623</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000820529864676</v>
+        <v>1.001000472799513</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1033707579525862</v>
+        <v>0.0373996491486291</v>
       </c>
       <c r="P25" t="n">
-        <v>143.2444958658998</v>
+        <v>165.3111390405115</v>
       </c>
       <c r="Q25" t="n">
-        <v>224.9091761320692</v>
+        <v>257.9457017304948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_8_24</t>
+          <t>model_23_8_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9985198670627017</v>
+        <v>0.9974511749760967</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7710878298513866</v>
+        <v>0.7241886182156341</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9937740730818823</v>
+        <v>0.9997404364647936</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9773494990155469</v>
+        <v>0.998284179319095</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9902733741569938</v>
+        <v>0.9994873726466524</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009897655767099245</v>
+        <v>0.001513092637697045</v>
       </c>
       <c r="H26" t="n">
-        <v>1.530736735827402</v>
+        <v>0.1637335506585181</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03112795981327963</v>
+        <v>7.790234148206691e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03069679671217711</v>
+        <v>0.0003473381951857936</v>
       </c>
       <c r="K26" t="n">
-        <v>0.03091230557294906</v>
+        <v>0.0002126182345727558</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1906499767730803</v>
+        <v>0.02419359792703454</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09948696279965152</v>
+        <v>0.03889849145785792</v>
       </c>
       <c r="N26" t="n">
-        <v>1.00082612070919</v>
+        <v>1.001176380780263</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1037223287724367</v>
+        <v>0.04055448077019685</v>
       </c>
       <c r="P26" t="n">
-        <v>143.2309146821663</v>
+        <v>164.9871992364534</v>
       </c>
       <c r="Q26" t="n">
-        <v>224.8955949483357</v>
+        <v>257.6217619264366</v>
       </c>
     </row>
   </sheetData>
